--- a/Team-Data/2008-09/3-14-2008-09.xlsx
+++ b/Team-Data/2008-09/3-14-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -763,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -787,10 +854,10 @@
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.754</v>
+        <v>0.758</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -864,7 +931,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -873,55 +940,55 @@
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
         <v>22.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -957,19 +1024,19 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,10 +1057,10 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1046,7 +1113,7 @@
         <v>76.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1055,7 +1122,7 @@
         <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="O4" t="n">
         <v>17.7</v>
@@ -1070,13 +1137,13 @@
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V4" t="n">
         <v>15.5</v>
@@ -1085,37 +1152,37 @@
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1127,7 +1194,7 @@
         <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM4" t="n">
         <v>22</v>
@@ -1145,13 +1212,13 @@
         <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AU4" t="n">
         <v>12</v>
@@ -1160,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -1222,31 +1289,31 @@
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
         <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
@@ -1261,10 +1328,10 @@
         <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
@@ -1276,16 +1343,16 @@
         <v>21.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1309,19 +1376,19 @@
         <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
         <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,7 +1397,7 @@
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
         <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.394</v>
+        <v>0.391</v>
       </c>
       <c r="O6" t="n">
         <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.755</v>
@@ -1440,34 +1507,34 @@
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.6</v>
+        <v>100.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1533,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1703,10 +1770,10 @@
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -1753,19 +1820,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H8" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I8" t="n">
         <v>36.7</v>
@@ -1780,34 +1847,34 @@
         <v>6.3</v>
       </c>
       <c r="M8" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V8" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.5</v>
@@ -1822,31 +1889,31 @@
         <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.8</v>
+        <v>102.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -1855,13 +1922,13 @@
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1876,7 +1943,7 @@
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1900,7 +1967,7 @@
         <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2025,7 +2092,7 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2043,25 +2110,25 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2219,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
@@ -2234,13 +2301,13 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2249,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="n">
         <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.632</v>
+        <v>0.642</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2329,16 +2396,16 @@
         <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P11" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
@@ -2353,40 +2420,40 @@
         <v>20.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
         <v>6.9</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG11" t="n">
         <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2398,7 +2465,7 @@
         <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2428,19 +2495,19 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2449,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>6</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>19</v>
@@ -2604,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2663,55 +2730,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J13" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R13" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U13" t="n">
         <v>21</v>
@@ -2720,16 +2787,16 @@
         <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA13" t="n">
         <v>19.8</v>
@@ -2741,7 +2808,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>27</v>
@@ -2774,22 +2841,22 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -2798,7 +2865,7 @@
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,16 +2874,16 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
         <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,40 +2930,40 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P14" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
         <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
         <v>13.5</v>
@@ -2914,28 +2981,28 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.5</v>
+        <v>108.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2986,13 +3053,13 @@
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3138,7 +3205,7 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H16" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.456</v>
@@ -3236,28 +3303,28 @@
         <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N16" t="n">
         <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.765</v>
+        <v>0.761</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
         <v>20.2</v>
@@ -3278,16 +3345,16 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3299,10 +3366,10 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
         <v>11</v>
@@ -3323,25 +3390,25 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3356,10 +3423,10 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0.448</v>
+        <v>0.441</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,46 +3476,46 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
         <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,25 +3524,25 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3484,7 +3551,7 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3499,22 +3566,22 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>19</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3573,61 +3640,61 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
         <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.303</v>
+        <v>0.292</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R18" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S18" t="n">
         <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
         <v>6.4</v>
@@ -3636,22 +3703,22 @@
         <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA18" t="n">
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.4</v>
+        <v>-4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
@@ -3675,16 +3742,16 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
@@ -3702,10 +3769,10 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV18" t="n">
         <v>17</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,13 +3912,13 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
@@ -3866,7 +3933,7 @@
         <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -3878,19 +3945,19 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
@@ -3902,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB19" t="n">
         <v>17</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>18</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="n">
         <v>41</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.631</v>
+        <v>0.641</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J20" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T20" t="n">
         <v>39.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V20" t="n">
         <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,28 +4070,28 @@
         <v>3.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA20" t="n">
         <v>20.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="n">
         <v>7</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4039,52 +4106,52 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP20" t="n">
         <v>23</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
@@ -4209,7 +4276,7 @@
         <v>19</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4245,25 +4312,25 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" t="n">
         <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>0.273</v>
+        <v>0.277</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4331,31 +4398,31 @@
         <v>11.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
         <v>20.3</v>
       </c>
       <c r="P22" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R22" t="n">
         <v>12.5</v>
       </c>
       <c r="S22" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T22" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V22" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W22" t="n">
         <v>7.2</v>
@@ -4367,7 +4434,7 @@
         <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA22" t="n">
         <v>20.8</v>
@@ -4376,10 +4443,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4415,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4427,10 +4494,10 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4442,13 +4509,13 @@
         <v>22</v>
       </c>
       <c r="AY22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
@@ -4609,16 +4676,16 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -4627,10 +4694,10 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -4758,10 +4825,10 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>16</v>
       </c>
       <c r="AK24" t="n">
         <v>13</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4809,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.53</v>
+        <v>0.523</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4886,13 +4953,13 @@
         <v>26.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
         <v>41.2</v>
@@ -4904,7 +4971,7 @@
         <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4922,10 +4989,10 @@
         <v>107.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4937,13 +5004,13 @@
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4964,16 +5031,16 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>4</v>
@@ -4994,7 +5061,7 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
         <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.641</v>
+        <v>0.631</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P26" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5077,7 +5144,7 @@
         <v>28.2</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5092,37 +5159,37 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG26" t="n">
         <v>8</v>
       </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>6</v>
-      </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,25 +5222,25 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5182,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5316,7 +5383,7 @@
         <v>12</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN27" t="n">
         <v>15</v>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS27" t="n">
         <v>25</v>
@@ -5340,16 +5407,16 @@
         <v>30</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>20</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5460,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
         <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.677</v>
+        <v>0.672</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J28" t="n">
         <v>79.7</v>
@@ -5420,10 +5487,10 @@
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
         <v>15.2</v>
@@ -5435,10 +5502,10 @@
         <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T28" t="n">
         <v>40.9</v>
@@ -5456,7 +5523,7 @@
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
         <v>18.8</v>
@@ -5465,13 +5532,13 @@
         <v>18.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC28" t="n">
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,7 +5553,7 @@
         <v>2</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>19</v>
@@ -5516,13 +5583,13 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>20</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5668,7 +5735,7 @@
         <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
         <v>18</v>
@@ -5683,10 +5750,10 @@
         <v>23</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP29" t="n">
         <v>28</v>
@@ -5704,16 +5771,16 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV29" t="n">
         <v>7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" t="n">
         <v>41</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.621</v>
+        <v>0.631</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.478</v>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O30" t="n">
         <v>21.6</v>
@@ -5802,16 +5869,16 @@
         <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
@@ -5820,40 +5887,40 @@
         <v>4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.5</v>
+        <v>103.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG30" t="n">
         <v>8</v>
       </c>
-      <c r="AF30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10</v>
-      </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>3</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>18</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
@@ -5898,19 +5965,19 @@
         <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB30" t="n">
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-14-2008-09</t>
+          <t>2009-03-14</t>
         </is>
       </c>
     </row>
